--- a/templates/Defect_Tracker_Filled.xlsx
+++ b/templates/Defect_Tracker_Filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc20060aec94d36e/Desktop/Multi-AI-Agent-Coding-Assistant/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc20060aec94d36e/Desktop/Multi-AI-Agent-Coding-Assistant - Copy(freebuff)/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_E4D3F04B11C85B87DAA0C4D89A555EF627FE8ABF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DFD4B771-DA31-4174-B416-12DE89EAF558}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_0A9B737F555A54AE977F4B1AB09728DA20E990D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6814B641-632B-46D8-8FC9-8B95C8DBA6D6}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="77">
   <si>
     <t>Sl No</t>
   </si>
@@ -107,6 +107,9 @@
     <t>Integrated JSON memory.</t>
   </si>
   <si>
+    <t>Muskan</t>
+  </si>
+  <si>
     <t>Project Analyzer missed nested folders.</t>
   </si>
   <si>
@@ -197,10 +200,58 @@
     <t>23-07-2026</t>
   </si>
   <si>
+    <t>01-08-2026</t>
+  </si>
+  <si>
+    <t>Uploaded file appeared multiple times in My Files.</t>
+  </si>
+  <si>
+    <t>Sprint 3</t>
+  </si>
+  <si>
+    <t>Added name+size dedupe in UserFiles.save and a proper uploader reset.</t>
+  </si>
+  <si>
+    <t>02-08-2026</t>
+  </si>
+  <si>
+    <t>Uploader reset raised StreamlitValueAssignmentNotAllowedError.</t>
+  </si>
+  <si>
+    <t>Reset uploaders by deleting widget keys before re-render.</t>
+  </si>
+  <si>
+    <t>03-08-2026</t>
+  </si>
+  <si>
+    <t>Analyse it with an uploaded file routed to the File tool.</t>
+  </si>
+  <si>
+    <t>Stripped attachment markers from intent classification and added terse routing keywords.</t>
+  </si>
+  <si>
+    <t>04-08-2026</t>
+  </si>
+  <si>
+    <t>Success rate KPI showed 100% with zero executions.</t>
+  </si>
+  <si>
+    <t>Success rate now reports 0 when there is no data.</t>
+  </si>
+  <si>
+    <t>Conversations KPI counted empty auto-created sessions.</t>
+  </si>
+  <si>
+    <t>Dashboard counts only conversations that contain messages.</t>
+  </si>
+  <si>
     <t>Others</t>
   </si>
   <si>
-    <t>Muskan</t>
+    <t>Generate documentation with an attached file routed to File/execution</t>
+  </si>
+  <si>
+    <t>Attachment markers no longer trigger file routing and documentation checked before file ops.</t>
   </si>
 </sst>
 </file>
@@ -210,7 +261,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -224,27 +275,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -328,47 +359,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -677,587 +690,719 @@
   <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="17.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.109375" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.44140625" style="3" customWidth="1"/>
-    <col min="4" max="4" width="42.109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="16" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.5546875" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="41.21875" style="3" customWidth="1"/>
-    <col min="9" max="10" width="21.88671875" style="3" customWidth="1"/>
-    <col min="11" max="11" width="46" style="3" customWidth="1"/>
-    <col min="12" max="14" width="17.5546875" style="3" customWidth="1"/>
-    <col min="15" max="16384" width="17.5546875" style="3"/>
+    <col min="1" max="1" width="6.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="47.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="15.88671875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="72.44140625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.88671875" style="2" customWidth="1"/>
+    <col min="10" max="11" width="21.109375" style="2" customWidth="1"/>
+    <col min="12" max="17" width="17.5546875" style="2" customWidth="1"/>
+    <col min="18" max="16384" width="17.5546875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="7">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="10">
+      <c r="B2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="7">
         <v>46204</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="H2" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="7">
         <v>46204</v>
       </c>
-      <c r="J2" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="11" t="s">
+      <c r="J2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="10">
+      <c r="B3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="7">
         <v>46205</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="7" t="s">
+      <c r="F3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H3" s="12" t="s">
+      <c r="H3" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="I3" s="10">
+      <c r="I3" s="7">
         <v>46207</v>
       </c>
-      <c r="J3" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="11" t="s">
+      <c r="J3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10">
+      <c r="B4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="7">
         <v>46210</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="7" t="s">
+      <c r="F4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="I4" s="10">
+      <c r="I4" s="7">
         <v>46211</v>
       </c>
-      <c r="J4" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="11" t="s">
+      <c r="J4" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K4" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="10">
+      <c r="B5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7">
         <v>46212</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="7" t="s">
+      <c r="F5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="I5" s="10">
+      <c r="I5" s="7">
         <v>46213</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="11" t="s">
+      <c r="J5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="8" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="7">
+        <v>46213</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="7">
+        <v>46214</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="8" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4">
+        <v>11</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="10">
-        <v>46213</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="7" t="s">
+      <c r="D15" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="I6" s="10">
-        <v>46214</v>
-      </c>
-      <c r="J6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="7" t="s">
+      <c r="H15" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="I15" s="8">
+        <v>46237</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="15.6" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="J7" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="11" t="s">
+      <c r="H17" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K17" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="7" t="s">
+    <row r="18" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="4">
+        <v>17</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="J8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="11" t="s">
+      <c r="H18" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K18" s="8" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="7" t="s">
+    <row r="19" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="11" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G10" s="7" t="s">
+      <c r="H19" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J10" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="7">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="J11" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="11" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="7">
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="B20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="H13" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K13" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="7">
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" s="11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="2"/>
-      <c r="B15" s="2"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="14"/>
-    </row>
-    <row r="16" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="4"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="16"/>
-    </row>
-    <row r="17" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="4"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="16"/>
-    </row>
-    <row r="18" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="4"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="5"/>
-      <c r="G18" s="4"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="16"/>
-    </row>
-    <row r="19" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2"/>
-      <c r="B19" s="2"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="14"/>
-    </row>
-    <row r="20" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="4"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="4"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="16"/>
+      <c r="H20" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I20" s="8">
+        <v>46239</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -1276,28 +1421,28 @@
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="5" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>50</v>
+      <c r="A3" s="5" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="5" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
-        <v>58</v>
+      <c r="A5" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>

--- a/templates/Defect_Tracker_Filled.xlsx
+++ b/templates/Defect_Tracker_Filled.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc20060aec94d36e/Desktop/Multi-AI-Agent-Coding-Assistant - Copy(freebuff)/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc20060aec94d36e/Desktop/Multi-AI-Agent-Coding-Assistant/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_0A9B737F555A54AE977F4B1AB09728DA20E990D3" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6814B641-632B-46D8-8FC9-8B95C8DBA6D6}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="11_5187136655EAD3C9E53A858F25B43FDA20E9CBCE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46EF0E08-7D11-4395-B2AA-C23C49AB907F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="97">
   <si>
     <t>Sl No</t>
   </si>
@@ -230,6 +230,12 @@
     <t>Stripped attachment markers from intent classification and added terse routing keywords.</t>
   </si>
   <si>
+    <t>Generate documentation with an attached file routed to File/execution</t>
+  </si>
+  <si>
+    <t>Attachment markers no longer trigger file routing and documentation checked before file ops.</t>
+  </si>
+  <si>
     <t>04-08-2026</t>
   </si>
   <si>
@@ -245,13 +251,67 @@
     <t>Dashboard counts only conversations that contain messages.</t>
   </si>
   <si>
+    <t>A request with attached content was routed by a keyword ('analyze') instead of the actual subject, so the attachment was ignored.</t>
+  </si>
+  <si>
+    <t>Sprint 4</t>
+  </si>
+  <si>
+    <t>Attached content takes priority over the generic analyze-to-code-analysis override; the experimental media feature was later removed.</t>
+  </si>
+  <si>
+    <t>Verified - then the experimental feature was removed.</t>
+  </si>
+  <si>
+    <t>"Analyze this project" with an uploaded ZIP reached the Code Analysis Agent instead of Project Analyzer.</t>
+  </si>
+  <si>
+    <t>Added a project-subject guard so project requests route to the Project Analyzer; code-snippet requests stay on Code Analysis.</t>
+  </si>
+  <si>
+    <t>"Analyze this Python code" with a pasted snippet and attached project was misrouted to Documentation.</t>
+  </si>
+  <si>
+    <t>Deterministic analyze-to-code-analysis pin runs before the LLM; verb matching uses only the user's own words, never pasted code or attachment listings.</t>
+  </si>
+  <si>
+    <t>Groq vision response displayed raw &lt;think&gt; reasoning or a truncated (reasoning-only) answer.</t>
+  </si>
+  <si>
+    <t>Strip think blocks before display and before the emptiness check so reasoning-only responses retry; raised the vision max_tokens budget.</t>
+  </si>
+  <si>
+    <t>"Also handle invalid non-numeric input" follow-up routed to the Patch Tool and tried a nonexistent file (calculator.py).</t>
+  </si>
+  <si>
+    <t>Added error-handling follow-up verbs (handle/validate/catch) and an invalid-to-debug override so the follow-up stays in the debugging conversation with its code context.</t>
+  </si>
+  <si>
+    <t>Markdown tables and long code blocks extended outside the chat message container.</t>
+  </si>
+  <si>
+    <t>Targeted CSS: table cells wrap long content, code blocks scroll horizontally inside the bubble.</t>
+  </si>
+  <si>
+    <t>Stale project report text (e.g. main.py -&gt; calculator.py) was injected into new, unrelated requests.</t>
+  </si>
+  <si>
+    <t>New topics strip the previous turn's blocks; attachments are scoped to the current message and replace old context.</t>
+  </si>
+  <si>
+    <t>The + menu exposed overlapping, experimental upload actions.</t>
+  </si>
+  <si>
+    <t>Consolidated uploads into a single Upload File action; ZIP archives are still extracted and analyzed as projects.</t>
+  </si>
+  <si>
+    <t>Provider rate-limit / LLM failures could surface raw tracebacks to the user.</t>
+  </si>
+  <si>
+    <t>LLM and tool errors are caught and shown as a friendly message while the real error is logged server-side.</t>
+  </si>
+  <si>
     <t>Others</t>
-  </si>
-  <si>
-    <t>Generate documentation with an attached file routed to File/execution</t>
-  </si>
-  <si>
-    <t>Attachment markers no longer trigger file routing and documentation checked before file ops.</t>
   </si>
 </sst>
 </file>
@@ -687,7 +747,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="17.5546875" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="6.109375" style="2" bestFit="1" customWidth="1"/>
@@ -697,11 +757,11 @@
     <col min="5" max="5" width="15.88671875" style="2" customWidth="1"/>
     <col min="6" max="6" width="12.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.5546875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="72.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="84.21875" style="2" customWidth="1"/>
     <col min="9" max="9" width="21.88671875" style="2" customWidth="1"/>
     <col min="10" max="11" width="21.109375" style="2" customWidth="1"/>
-    <col min="12" max="17" width="17.5546875" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="17.5546875" style="2"/>
+    <col min="12" max="18" width="17.5546875" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="17.5546875" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="1" customFormat="1" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
@@ -1219,7 +1279,7 @@
       <c r="H15" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="I15" s="8">
+      <c r="I15" s="7">
         <v>46237</v>
       </c>
       <c r="J15" s="4" t="s">
@@ -1310,7 +1370,7 @@
         <v>66</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>61</v>
@@ -1322,10 +1382,10 @@
         <v>19</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>16</v>
@@ -1342,10 +1402,10 @@
         <v>11</v>
       </c>
       <c r="C19" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>61</v>
@@ -1357,10 +1417,10 @@
         <v>19</v>
       </c>
       <c r="H19" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="I19" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="I19" s="8" t="s">
-        <v>69</v>
       </c>
       <c r="J19" s="4" t="s">
         <v>16</v>
@@ -1377,10 +1437,10 @@
         <v>11</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>61</v>
@@ -1392,15 +1452,330 @@
         <v>19</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="I20" s="8">
+        <v>75</v>
+      </c>
+      <c r="I20" s="7">
         <v>46239</v>
       </c>
       <c r="J20" s="4" t="s">
         <v>16</v>
       </c>
       <c r="K20" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" s="7">
+        <v>46241</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="I21" s="7">
+        <v>46242</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="4">
+        <v>21</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" s="7">
+        <v>46243</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="I22" s="7">
+        <v>46243</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C23" s="7">
+        <v>46244</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F23" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G23" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="I23" s="7">
+        <v>46244</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="7">
+        <v>46245</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H24" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="7">
+        <v>46246</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="7">
+        <v>46247</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="I25" s="7">
+        <v>46248</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="4">
+        <v>25</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="7">
+        <v>46248</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G26" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H26" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="I26" s="7">
+        <v>46248</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K26" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C27" s="7">
+        <v>46248</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F27" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G27" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="I27" s="7">
+        <v>46249</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K27" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="30.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C28" s="7">
+        <v>46249</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="H28" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="I28" s="7">
+        <v>46250</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K28" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="32.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C29" s="7">
+        <v>46250</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G29" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="H29" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="I29" s="7">
+        <v>46251</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K29" s="8" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1442,7 +1817,7 @@
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
-        <v>74</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
